--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260501.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260501.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -46,21 +46,12 @@
     <t>6301.T</t>
   </si>
   <si>
-    <t>7974.T</t>
-  </si>
-  <si>
-    <t>8346.T</t>
-  </si>
-  <si>
     <t>8360.T</t>
   </si>
   <si>
     <t>A17U</t>
   </si>
   <si>
-    <t>APD</t>
-  </si>
-  <si>
     <t>AVAV</t>
   </si>
   <si>
@@ -91,18 +82,12 @@
     <t>CEG</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
     <t>CLSE</t>
   </si>
   <si>
     <t>CME</t>
   </si>
   <si>
-    <t>CNQ</t>
-  </si>
-  <si>
     <t>CNXT</t>
   </si>
   <si>
@@ -112,9 +97,6 @@
     <t>COLO</t>
   </si>
   <si>
-    <t>COPX</t>
-  </si>
-  <si>
     <t>CSCO</t>
   </si>
   <si>
@@ -154,9 +136,6 @@
     <t>GEV</t>
   </si>
   <si>
-    <t>GIS</t>
-  </si>
-  <si>
     <t>HGER</t>
   </si>
   <si>
@@ -178,9 +157,6 @@
     <t>LAC</t>
   </si>
   <si>
-    <t>LIN</t>
-  </si>
-  <si>
     <t>LLY</t>
   </si>
   <si>
@@ -190,15 +166,9 @@
     <t>MELI</t>
   </si>
   <si>
-    <t>MSFT</t>
-  </si>
-  <si>
     <t>NOC</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
     <t>NVO</t>
   </si>
   <si>
@@ -211,9 +181,6 @@
     <t>PKB</t>
   </si>
   <si>
-    <t>PLTR</t>
-  </si>
-  <si>
     <t>PM</t>
   </si>
   <si>
@@ -289,13 +256,7 @@
     <t>SHYG</t>
   </si>
   <si>
-    <t>TLT</t>
-  </si>
-  <si>
     <t>AGQ</t>
-  </si>
-  <si>
-    <t>GDX</t>
   </si>
   <si>
     <t>IAUM</t>
@@ -695,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -735,25 +696,25 @@
         <v>2000</v>
       </c>
       <c r="C2">
-        <v>30.94</v>
+        <v>33.04</v>
       </c>
       <c r="D2">
-        <v>-112.31</v>
+        <v>137.88</v>
       </c>
       <c r="E2">
-        <v>61880</v>
+        <v>66080</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H2">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I2">
-        <v>7895.89</v>
+        <v>8438.42</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -764,25 +725,25 @@
         <v>427000</v>
       </c>
       <c r="C3">
-        <v>13.17</v>
+        <v>12.87</v>
       </c>
       <c r="D3">
-        <v>-6539.25</v>
+        <v>-28893</v>
       </c>
       <c r="E3">
-        <v>5623590</v>
+        <v>5495490</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H3">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I3">
-        <v>717570.08</v>
+        <v>701774.0699999999</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -793,25 +754,25 @@
         <v>6000</v>
       </c>
       <c r="C4">
-        <v>6.17</v>
+        <v>5.94</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-107.24</v>
       </c>
       <c r="E4">
-        <v>37020</v>
+        <v>35640</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H4">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I4">
-        <v>4723.75</v>
+        <v>4551.23</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -822,25 +783,25 @@
         <v>6000</v>
       </c>
       <c r="C5">
-        <v>7.18</v>
+        <v>6.92</v>
       </c>
       <c r="D5">
-        <v>-30.63</v>
+        <v>-84.26000000000001</v>
       </c>
       <c r="E5">
-        <v>43080</v>
+        <v>41520</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H5">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I5">
-        <v>5497.01</v>
+        <v>5302.1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -851,25 +812,25 @@
         <v>2000</v>
       </c>
       <c r="C6">
-        <v>35.92</v>
+        <v>35.72</v>
       </c>
       <c r="D6">
-        <v>-153.14</v>
+        <v>163.42</v>
       </c>
       <c r="E6">
-        <v>71840</v>
+        <v>71440</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H6">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I6">
-        <v>9166.780000000001</v>
+        <v>9122.889999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -880,25 +841,25 @@
         <v>200</v>
       </c>
       <c r="C7">
-        <v>29.92</v>
+        <v>30.98</v>
       </c>
       <c r="D7">
-        <v>-30.12</v>
+        <v>50.05</v>
       </c>
       <c r="E7">
-        <v>5984</v>
+        <v>6196</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H7">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I7">
-        <v>763.5599999999999</v>
+        <v>791.23</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -909,25 +870,25 @@
         <v>300</v>
       </c>
       <c r="C8">
-        <v>143.1</v>
+        <v>137.4</v>
       </c>
       <c r="D8">
-        <v>654.6900000000001</v>
+        <v>53.62</v>
       </c>
       <c r="E8">
-        <v>42930</v>
+        <v>41220</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H8">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I8">
-        <v>5477.87</v>
+        <v>5263.79</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -938,25 +899,25 @@
         <v>2000</v>
       </c>
       <c r="C9">
-        <v>25.98</v>
+        <v>26.24</v>
       </c>
       <c r="D9">
-        <v>-66.36</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="E9">
-        <v>51960</v>
+        <v>52480</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H9">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I9">
-        <v>6630.1</v>
+        <v>6701.7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -967,25 +928,25 @@
         <v>600</v>
       </c>
       <c r="C10">
-        <v>88.45999999999999</v>
+        <v>89.98</v>
       </c>
       <c r="D10">
-        <v>-102.61</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E10">
-        <v>53076</v>
+        <v>53988</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H10">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I10">
-        <v>6772.5</v>
+        <v>6894.27</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -996,25 +957,25 @@
         <v>110000</v>
       </c>
       <c r="C11">
-        <v>35.36</v>
+        <v>35.8</v>
       </c>
       <c r="D11">
-        <v>-12072.85</v>
+        <v>1685.24</v>
       </c>
       <c r="E11">
-        <v>3889600</v>
+        <v>3938000</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H11">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I11">
-        <v>496312.96</v>
+        <v>502882.6</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1025,25 +986,25 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>10.15</v>
+        <v>10.46</v>
       </c>
       <c r="D12">
-        <v>-22.33</v>
+        <v>17.87</v>
       </c>
       <c r="E12">
-        <v>7105</v>
+        <v>7322</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H12">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I12">
-        <v>906.6</v>
+        <v>935.02</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1054,25 +1015,25 @@
         <v>4700</v>
       </c>
       <c r="C13">
-        <v>629</v>
+        <v>631.5</v>
       </c>
       <c r="D13">
-        <v>-27891.35</v>
+        <v>14101.15</v>
       </c>
       <c r="E13">
-        <v>2956300</v>
+        <v>2968050</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H13">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I13">
-        <v>377223.88</v>
+        <v>379019.99</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1083,25 +1044,25 @@
         <v>23500</v>
       </c>
       <c r="C14">
-        <v>407.6</v>
+        <v>415</v>
       </c>
       <c r="D14">
-        <v>-13195.91</v>
+        <v>7800.64</v>
       </c>
       <c r="E14">
-        <v>9578600</v>
+        <v>9752500</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H14">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I14">
-        <v>1222229.36</v>
+        <v>1245394.25</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1112,25 +1073,25 @@
         <v>4000</v>
       </c>
       <c r="C15">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>15.32</v>
       </c>
       <c r="E15">
-        <v>20480</v>
+        <v>20360</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H15">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I15">
-        <v>2613.25</v>
+        <v>2599.97</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1141,25 +1102,25 @@
         <v>35300</v>
       </c>
       <c r="C16">
-        <v>6856</v>
+        <v>6514</v>
       </c>
       <c r="D16">
-        <v>-43567.44</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>242016800</v>
+        <v>229944200</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H16">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="I16">
-        <v>1524705.84</v>
+        <v>1471642.88</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1170,25 +1131,25 @@
         <v>200</v>
       </c>
       <c r="C17">
-        <v>473.8</v>
+        <v>473</v>
       </c>
       <c r="D17">
-        <v>-122.52</v>
+        <v>132.78</v>
       </c>
       <c r="E17">
-        <v>94760</v>
+        <v>94600</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H17">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I17">
-        <v>12091.38</v>
+        <v>12080.42</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1199,25 +1160,25 @@
         <v>16000</v>
       </c>
       <c r="C18">
-        <v>7.3</v>
+        <v>7.34</v>
       </c>
       <c r="D18">
-        <v>-61.26</v>
+        <v>40.85</v>
       </c>
       <c r="E18">
-        <v>116800</v>
+        <v>117440</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H18">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I18">
-        <v>14903.68</v>
+        <v>14997.09</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1225,173 +1186,173 @@
         <v>10</v>
       </c>
       <c r="B19">
-        <v>18700</v>
+        <v>2100</v>
       </c>
       <c r="C19">
-        <v>7922</v>
+        <v>5390</v>
       </c>
       <c r="D19">
-        <v>3397.51</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>148141400</v>
+        <v>11319000</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H19">
-        <v>0.0063</v>
+        <v>0.0064</v>
       </c>
       <c r="I19">
-        <v>933290.8199999999</v>
+        <v>72441.60000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>11</v>
+      <c r="A20">
+        <v>857</v>
       </c>
       <c r="B20">
-        <v>18000</v>
+        <v>342000</v>
       </c>
       <c r="C20">
-        <v>689</v>
+        <v>11.7</v>
       </c>
       <c r="D20">
-        <v>4398.03</v>
+        <v>-14408.84</v>
       </c>
       <c r="E20">
-        <v>12402000</v>
+        <v>4001400</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H20">
-        <v>0.0063</v>
+        <v>0.1277</v>
       </c>
       <c r="I20">
-        <v>78132.60000000001</v>
+        <v>510978.78</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>12</v>
+      <c r="A21">
+        <v>883</v>
       </c>
       <c r="B21">
-        <v>2100</v>
+        <v>106000</v>
       </c>
       <c r="C21">
-        <v>5500</v>
+        <v>28.62</v>
       </c>
       <c r="D21">
-        <v>4736.34</v>
+        <v>-10285.1</v>
       </c>
       <c r="E21">
-        <v>11550000</v>
+        <v>3033720</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H21">
-        <v>0.0063</v>
+        <v>0.1277</v>
       </c>
       <c r="I21">
-        <v>72765</v>
+        <v>387406.04</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>857</v>
+        <v>9633</v>
       </c>
       <c r="B22">
-        <v>342000</v>
+        <v>1800</v>
       </c>
       <c r="C22">
-        <v>11.67</v>
+        <v>46.36</v>
       </c>
       <c r="D22">
-        <v>9165.67</v>
+        <v>-101.11</v>
       </c>
       <c r="E22">
-        <v>3991140</v>
+        <v>83448</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H22">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="I22">
-        <v>509269.46</v>
+        <v>10656.31</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23">
-        <v>883</v>
+      <c r="A23" t="s">
+        <v>11</v>
       </c>
       <c r="B23">
-        <v>106000</v>
+        <v>6000</v>
       </c>
       <c r="C23">
-        <v>28.98</v>
+        <v>2.51</v>
       </c>
       <c r="D23">
-        <v>7304.97</v>
+        <v>93.95</v>
       </c>
       <c r="E23">
-        <v>3071880</v>
+        <v>15060</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H23">
-        <v>0.1276</v>
+        <v>0.7829</v>
       </c>
       <c r="I23">
-        <v>391971.89</v>
+        <v>11790.47</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24">
-        <v>9633</v>
+      <c r="A24" t="s">
+        <v>12</v>
       </c>
       <c r="B24">
-        <v>1800</v>
+        <v>1362</v>
       </c>
       <c r="C24">
-        <v>46.5</v>
+        <v>180.26</v>
       </c>
       <c r="D24">
-        <v>-96.48</v>
+        <v>-6415.02</v>
       </c>
       <c r="E24">
-        <v>83700</v>
+        <v>245514.12</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H24">
-        <v>0.1276</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>10680.12</v>
+        <v>245514.12</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1399,28 +1360,28 @@
         <v>13</v>
       </c>
       <c r="B25">
-        <v>6000</v>
+        <v>18900</v>
       </c>
       <c r="C25">
-        <v>2.52</v>
+        <v>104.74</v>
       </c>
       <c r="D25">
-        <v>-93.97</v>
+        <v>-16443</v>
       </c>
       <c r="E25">
-        <v>15120</v>
+        <v>1979586</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H25">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>11840.47</v>
+        <v>1979586</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1428,28 +1389,28 @@
         <v>14</v>
       </c>
       <c r="B26">
-        <v>3520</v>
+        <v>22075</v>
       </c>
       <c r="C26">
-        <v>303.35</v>
+        <v>90.38</v>
       </c>
       <c r="D26">
-        <v>3414.4</v>
+        <v>-3311.25</v>
       </c>
       <c r="E26">
-        <v>1067792</v>
+        <v>1995138.5</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1067792</v>
+        <v>1995138.5</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1457,28 +1418,28 @@
         <v>15</v>
       </c>
       <c r="B27">
-        <v>1362</v>
+        <v>14660</v>
       </c>
       <c r="C27">
-        <v>192.34</v>
+        <v>118.56</v>
       </c>
       <c r="D27">
-        <v>-4630.8</v>
+        <v>-20524</v>
       </c>
       <c r="E27">
-        <v>261967.08</v>
+        <v>1738089.6</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>261967.08</v>
+        <v>1738089.6</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1486,28 +1447,28 @@
         <v>16</v>
       </c>
       <c r="B28">
-        <v>18900</v>
+        <v>14901</v>
       </c>
       <c r="C28">
-        <v>104.65</v>
+        <v>133.27</v>
       </c>
       <c r="D28">
-        <v>1701</v>
+        <v>26374.77</v>
       </c>
       <c r="E28">
-        <v>1977885</v>
+        <v>1985856.27</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1977885</v>
+        <v>1985856.27</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1515,28 +1476,28 @@
         <v>17</v>
       </c>
       <c r="B29">
-        <v>22075</v>
+        <v>70</v>
       </c>
       <c r="C29">
-        <v>88.81999999999999</v>
+        <v>22.79</v>
       </c>
       <c r="D29">
-        <v>-14790.25</v>
+        <v>63.7</v>
       </c>
       <c r="E29">
-        <v>1960701.5</v>
+        <v>1595.3</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1960701.5</v>
+        <v>1595.3</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1544,28 +1505,28 @@
         <v>18</v>
       </c>
       <c r="B30">
-        <v>14660</v>
+        <v>3000</v>
       </c>
       <c r="C30">
-        <v>119.44</v>
+        <v>10.87</v>
       </c>
       <c r="D30">
-        <v>-2492.2</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1750990.4</v>
+        <v>32610</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I30">
-        <v>1750990.4</v>
+        <v>25530.37</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1573,28 +1534,28 @@
         <v>19</v>
       </c>
       <c r="B31">
-        <v>14901</v>
+        <v>821</v>
       </c>
       <c r="C31">
-        <v>130.85</v>
+        <v>216.68</v>
       </c>
       <c r="D31">
-        <v>-24884.67</v>
+        <v>303.77</v>
       </c>
       <c r="E31">
-        <v>1949795.85</v>
+        <v>177894.28</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1949795.85</v>
+        <v>177894.28</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1602,28 +1563,28 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="C32">
-        <v>21.48</v>
+        <v>6.27</v>
       </c>
       <c r="D32">
-        <v>-4.9</v>
+        <v>-3.13</v>
       </c>
       <c r="E32">
-        <v>1503.6</v>
+        <v>1254</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I32">
-        <v>1503.6</v>
+        <v>981.76</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1631,28 +1592,28 @@
         <v>21</v>
       </c>
       <c r="B33">
-        <v>3000</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>10.89</v>
+        <v>321.05</v>
       </c>
       <c r="D33">
-        <v>-140.95</v>
+        <v>198.6</v>
       </c>
       <c r="E33">
-        <v>32670</v>
+        <v>4815.75</v>
       </c>
       <c r="F33" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H33">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>25583.88</v>
+        <v>4815.75</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1660,28 +1621,28 @@
         <v>22</v>
       </c>
       <c r="B34">
-        <v>821</v>
+        <v>659624</v>
       </c>
       <c r="C34">
-        <v>216.18</v>
+        <v>31.45</v>
       </c>
       <c r="D34">
-        <v>-4835.69</v>
+        <v>19788.72</v>
       </c>
       <c r="E34">
-        <v>177483.78</v>
+        <v>20745174.8</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>177483.78</v>
+        <v>20745174.8</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1689,28 +1650,28 @@
         <v>23</v>
       </c>
       <c r="B35">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="C35">
-        <v>6.36</v>
+        <v>290.29</v>
       </c>
       <c r="D35">
-        <v>-1.57</v>
+        <v>21.75</v>
       </c>
       <c r="E35">
-        <v>1272</v>
+        <v>8418.41</v>
       </c>
       <c r="F35" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H35">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>996.1</v>
+        <v>8418.41</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1718,28 +1679,28 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <v>15</v>
+        <v>103455</v>
       </c>
       <c r="C36">
-        <v>305.71</v>
+        <v>52.88</v>
       </c>
       <c r="D36">
-        <v>-141.9</v>
+        <v>-52762.05</v>
       </c>
       <c r="E36">
-        <v>4585.65</v>
+        <v>5470700.4</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>4585.65</v>
+        <v>5470700.4</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1747,28 +1708,28 @@
         <v>25</v>
       </c>
       <c r="B37">
-        <v>8000</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>122.31</v>
+        <v>202.99</v>
       </c>
       <c r="D37">
-        <v>-10560</v>
+        <v>58.7</v>
       </c>
       <c r="E37">
-        <v>978480</v>
+        <v>1014.95</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>978480</v>
+        <v>1014.95</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1776,28 +1737,28 @@
         <v>26</v>
       </c>
       <c r="B38">
-        <v>659624</v>
+        <v>45862</v>
       </c>
       <c r="C38">
-        <v>31.02</v>
+        <v>37.45</v>
       </c>
       <c r="D38">
-        <v>-138521.04</v>
+        <v>-35772.36</v>
       </c>
       <c r="E38">
-        <v>20461536.48</v>
+        <v>1717531.9</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>20461536.48</v>
+        <v>1717531.9</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1805,28 +1766,28 @@
         <v>27</v>
       </c>
       <c r="B39">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>284.53</v>
+        <v>92.63</v>
       </c>
       <c r="D39">
-        <v>75.11</v>
+        <v>10.14</v>
       </c>
       <c r="E39">
-        <v>8251.370000000001</v>
+        <v>1204.19</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>8251.370000000001</v>
+        <v>1204.19</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1834,28 +1795,28 @@
         <v>28</v>
       </c>
       <c r="B40">
-        <v>27000</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>46.36</v>
+        <v>166.89</v>
       </c>
       <c r="D40">
-        <v>36180</v>
+        <v>-27.2</v>
       </c>
       <c r="E40">
-        <v>1251720</v>
+        <v>1668.9</v>
       </c>
       <c r="F40" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1251720</v>
+        <v>1668.9</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1863,28 +1824,28 @@
         <v>29</v>
       </c>
       <c r="B41">
-        <v>103455</v>
+        <v>361</v>
       </c>
       <c r="C41">
-        <v>50.8</v>
+        <v>192.28</v>
       </c>
       <c r="D41">
-        <v>-43523.52</v>
+        <v>595.65</v>
       </c>
       <c r="E41">
-        <v>5255514</v>
+        <v>69413.08</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>5255514</v>
+        <v>69413.08</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1892,28 +1853,28 @@
         <v>30</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>800</v>
       </c>
       <c r="C42">
-        <v>194.1</v>
+        <v>58.6</v>
       </c>
       <c r="D42">
-        <v>-12.9</v>
+        <v>62.63</v>
       </c>
       <c r="E42">
-        <v>970.5</v>
+        <v>46880</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I42">
-        <v>970.5</v>
+        <v>36702.35</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1921,28 +1882,28 @@
         <v>31</v>
       </c>
       <c r="B43">
-        <v>45862</v>
+        <v>612026</v>
       </c>
       <c r="C43">
-        <v>38.68</v>
+        <v>30.7</v>
       </c>
       <c r="D43">
-        <v>-32562.02</v>
+        <v>104044.42</v>
       </c>
       <c r="E43">
-        <v>1773942.16</v>
+        <v>18789198.2</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>1773942.16</v>
+        <v>18789198.2</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1950,28 +1911,28 @@
         <v>32</v>
       </c>
       <c r="B44">
-        <v>22500</v>
+        <v>401</v>
       </c>
       <c r="C44">
-        <v>78.69</v>
+        <v>578.39</v>
       </c>
       <c r="D44">
-        <v>-67725</v>
+        <v>453.13</v>
       </c>
       <c r="E44">
-        <v>1770525</v>
+        <v>231934.39</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>1770525</v>
+        <v>231934.39</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1979,28 +1940,28 @@
         <v>33</v>
       </c>
       <c r="B45">
-        <v>13</v>
+        <v>5000</v>
       </c>
       <c r="C45">
-        <v>86.86</v>
+        <v>114.48</v>
       </c>
       <c r="D45">
-        <v>-18.2</v>
+        <v>250</v>
       </c>
       <c r="E45">
-        <v>1129.18</v>
+        <v>572400</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>1129.18</v>
+        <v>572400</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2008,28 +1969,28 @@
         <v>34</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>174.22</v>
+        <v>100.7</v>
       </c>
       <c r="D46">
-        <v>1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="E46">
-        <v>1742.2</v>
+        <v>100.7</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1742.2</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2037,28 +1998,28 @@
         <v>35</v>
       </c>
       <c r="B47">
-        <v>361</v>
+        <v>36</v>
       </c>
       <c r="C47">
-        <v>188.36</v>
+        <v>135.46</v>
       </c>
       <c r="D47">
-        <v>1292.38</v>
+        <v>-71.64</v>
       </c>
       <c r="E47">
-        <v>67997.96000000001</v>
+        <v>4876.56</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>67997.96000000001</v>
+        <v>4876.56</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2066,28 +2027,28 @@
         <v>36</v>
       </c>
       <c r="B48">
-        <v>800</v>
+        <v>17</v>
       </c>
       <c r="C48">
-        <v>56.75</v>
+        <v>422.44</v>
       </c>
       <c r="D48">
-        <v>-25.06</v>
+        <v>-52.87</v>
       </c>
       <c r="E48">
-        <v>45400</v>
+        <v>7181.48</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H48">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>35552.74</v>
+        <v>7181.48</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2095,28 +2056,28 @@
         <v>37</v>
       </c>
       <c r="B49">
-        <v>612026</v>
+        <v>30900</v>
       </c>
       <c r="C49">
-        <v>30.72</v>
+        <v>163.59</v>
       </c>
       <c r="D49">
-        <v>61202.6</v>
+        <v>49131</v>
       </c>
       <c r="E49">
-        <v>18801438.72</v>
+        <v>5054931</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>18801438.72</v>
+        <v>5054931</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2124,28 +2085,28 @@
         <v>38</v>
       </c>
       <c r="B50">
-        <v>401</v>
+        <v>76000</v>
       </c>
       <c r="C50">
-        <v>563.86</v>
+        <v>39.04</v>
       </c>
       <c r="D50">
-        <v>-1535.83</v>
+        <v>-29640</v>
       </c>
       <c r="E50">
-        <v>226107.86</v>
+        <v>2967040</v>
       </c>
       <c r="F50" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>226107.86</v>
+        <v>2967040</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2153,28 +2114,28 @@
         <v>39</v>
       </c>
       <c r="B51">
-        <v>5000</v>
+        <v>1662</v>
       </c>
       <c r="C51">
-        <v>115.82</v>
+        <v>1073.95</v>
       </c>
       <c r="D51">
-        <v>-7650</v>
+        <v>18282</v>
       </c>
       <c r="E51">
-        <v>579100</v>
+        <v>1784904.9</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>579100</v>
+        <v>1784904.9</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2182,28 +2143,28 @@
         <v>40</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>626620</v>
       </c>
       <c r="C52">
-        <v>100.96</v>
+        <v>32.69</v>
       </c>
       <c r="D52">
-        <v>-0.42</v>
+        <v>206784.6</v>
       </c>
       <c r="E52">
-        <v>100.96</v>
+        <v>20484207.8</v>
       </c>
       <c r="F52" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>100.96</v>
+        <v>20484207.8</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2211,28 +2172,28 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C53">
-        <v>138.42</v>
+        <v>156.44</v>
       </c>
       <c r="D53">
-        <v>-109.8</v>
+        <v>70.98</v>
       </c>
       <c r="E53">
-        <v>4983.12</v>
+        <v>6570.48</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>4983.12</v>
+        <v>6570.48</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2240,28 +2201,28 @@
         <v>42</v>
       </c>
       <c r="B54">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>413.07</v>
+        <v>307.65</v>
       </c>
       <c r="D54">
-        <v>-62.9</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="E54">
-        <v>7022.19</v>
+        <v>6153</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>7022.19</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2269,28 +2230,28 @@
         <v>43</v>
       </c>
       <c r="B55">
-        <v>30900</v>
+        <v>611583</v>
       </c>
       <c r="C55">
-        <v>154.37</v>
+        <v>29.46</v>
       </c>
       <c r="D55">
-        <v>-72924</v>
+        <v>79505.78999999999</v>
       </c>
       <c r="E55">
-        <v>4770033</v>
+        <v>18017235.18</v>
       </c>
       <c r="F55" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55">
-        <v>4770033</v>
+        <v>18017235.18</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2298,28 +2259,28 @@
         <v>44</v>
       </c>
       <c r="B56">
-        <v>76000</v>
+        <v>3800</v>
       </c>
       <c r="C56">
-        <v>39.69</v>
+        <v>621.77</v>
       </c>
       <c r="D56">
-        <v>-15200</v>
+        <v>72542</v>
       </c>
       <c r="E56">
-        <v>3016440</v>
+        <v>2362726</v>
       </c>
       <c r="F56" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>3016440</v>
+        <v>2362726</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2327,28 +2288,28 @@
         <v>45</v>
       </c>
       <c r="B57">
-        <v>1662</v>
+        <v>1451</v>
       </c>
       <c r="C57">
-        <v>1088.93</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D57">
-        <v>-52020.6</v>
+        <v>-1204.33</v>
       </c>
       <c r="E57">
-        <v>1809801.66</v>
+        <v>100104.49</v>
       </c>
       <c r="F57" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>1809801.66</v>
+        <v>100104.49</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2356,28 +2317,28 @@
         <v>46</v>
       </c>
       <c r="B58">
-        <v>21300</v>
+        <v>1794</v>
       </c>
       <c r="C58">
-        <v>34.75</v>
+        <v>5.54</v>
       </c>
       <c r="D58">
-        <v>639</v>
+        <v>-304.98</v>
       </c>
       <c r="E58">
-        <v>740175</v>
+        <v>9938.76</v>
       </c>
       <c r="F58" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>740175</v>
+        <v>9938.76</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2385,28 +2346,28 @@
         <v>47</v>
       </c>
       <c r="B59">
-        <v>611000</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>31.99</v>
+        <v>967.9299999999999</v>
       </c>
       <c r="D59">
-        <v>36660</v>
+        <v>13.8</v>
       </c>
       <c r="E59">
-        <v>19545890</v>
+        <v>2903.79</v>
       </c>
       <c r="F59" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>19545890</v>
+        <v>2903.79</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2414,28 +2375,28 @@
         <v>48</v>
       </c>
       <c r="B60">
-        <v>42</v>
+        <v>8000</v>
       </c>
       <c r="C60">
-        <v>156.3</v>
+        <v>1.96</v>
       </c>
       <c r="D60">
-        <v>-27.3</v>
+        <v>-62.63</v>
       </c>
       <c r="E60">
-        <v>6564.6</v>
+        <v>15680</v>
       </c>
       <c r="F60" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I60">
-        <v>6564.6</v>
+        <v>12275.87</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2443,28 +2404,28 @@
         <v>49</v>
       </c>
       <c r="B61">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C61">
-        <v>311.45</v>
+        <v>1813.53</v>
       </c>
       <c r="D61">
-        <v>-3.6</v>
+        <v>-2994.64</v>
       </c>
       <c r="E61">
-        <v>6229</v>
+        <v>148709.46</v>
       </c>
       <c r="F61" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>6229</v>
+        <v>148709.46</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2472,28 +2433,28 @@
         <v>50</v>
       </c>
       <c r="B62">
-        <v>558200</v>
+        <v>2747</v>
       </c>
       <c r="C62">
-        <v>29.47</v>
+        <v>567</v>
       </c>
       <c r="D62">
-        <v>145132</v>
+        <v>-3131.58</v>
       </c>
       <c r="E62">
-        <v>16450154</v>
+        <v>1557549</v>
       </c>
       <c r="F62" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>16450154</v>
+        <v>1557549</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2501,28 +2462,28 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>3800</v>
+        <v>18100</v>
       </c>
       <c r="C63">
-        <v>525.8099999999999</v>
+        <v>44.39</v>
       </c>
       <c r="D63">
-        <v>-95722</v>
+        <v>9231</v>
       </c>
       <c r="E63">
-        <v>1998078</v>
+        <v>803459</v>
       </c>
       <c r="F63" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1998078</v>
+        <v>803459</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2530,28 +2491,28 @@
         <v>52</v>
       </c>
       <c r="B64">
-        <v>1451</v>
+        <v>100</v>
       </c>
       <c r="C64">
-        <v>70.37</v>
+        <v>63.45</v>
       </c>
       <c r="D64">
-        <v>435.3</v>
+        <v>-36</v>
       </c>
       <c r="E64">
-        <v>102106.87</v>
+        <v>6345</v>
       </c>
       <c r="F64" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>102106.87</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2559,28 +2520,28 @@
         <v>53</v>
       </c>
       <c r="B65">
-        <v>1794</v>
+        <v>34</v>
       </c>
       <c r="C65">
-        <v>4.92</v>
+        <v>184.56</v>
       </c>
       <c r="D65">
-        <v>-592.02</v>
+        <v>118.32</v>
       </c>
       <c r="E65">
-        <v>8826.48</v>
+        <v>6275.04</v>
       </c>
       <c r="F65" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>8826.48</v>
+        <v>6275.04</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2588,28 +2549,28 @@
         <v>54</v>
       </c>
       <c r="B66">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>510.29</v>
+        <v>107</v>
       </c>
       <c r="D66">
-        <v>-1840</v>
+        <v>-17.5</v>
       </c>
       <c r="E66">
-        <v>2041160</v>
+        <v>1070</v>
       </c>
       <c r="F66" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>2041160</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2617,28 +2578,28 @@
         <v>55</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>8810</v>
       </c>
       <c r="C67">
-        <v>874</v>
+        <v>169.19</v>
       </c>
       <c r="D67">
-        <v>17.19</v>
+        <v>24756.1</v>
       </c>
       <c r="E67">
-        <v>2622</v>
+        <v>1490563.9</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>2622</v>
+        <v>1490563.9</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2646,28 +2607,28 @@
         <v>56</v>
       </c>
       <c r="B68">
-        <v>8000</v>
+        <v>24680</v>
       </c>
       <c r="C68">
-        <v>2.06</v>
+        <v>672.88</v>
       </c>
       <c r="D68">
-        <v>62.65</v>
+        <v>-31343.6</v>
       </c>
       <c r="E68">
-        <v>16480</v>
+        <v>16606678.4</v>
       </c>
       <c r="F68" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H68">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>12905.49</v>
+        <v>16606678.4</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2675,28 +2636,28 @@
         <v>57</v>
       </c>
       <c r="B69">
-        <v>82</v>
+        <v>3800</v>
       </c>
       <c r="C69">
-        <v>1791.99</v>
+        <v>47.57</v>
       </c>
       <c r="D69">
-        <v>-3877.78</v>
+        <v>9272</v>
       </c>
       <c r="E69">
-        <v>146943.18</v>
+        <v>180766</v>
       </c>
       <c r="F69" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69">
-        <v>146943.18</v>
+        <v>180766</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2704,28 +2665,28 @@
         <v>58</v>
       </c>
       <c r="B70">
-        <v>6440</v>
+        <v>9000</v>
       </c>
       <c r="C70">
-        <v>429.25</v>
+        <v>102.12</v>
       </c>
       <c r="D70">
-        <v>28529.2</v>
+        <v>-39600</v>
       </c>
       <c r="E70">
-        <v>2764370</v>
+        <v>919080</v>
       </c>
       <c r="F70" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>2764370</v>
+        <v>919080</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2733,28 +2694,28 @@
         <v>59</v>
       </c>
       <c r="B71">
-        <v>2747</v>
+        <v>1820</v>
       </c>
       <c r="C71">
-        <v>577.8200000000001</v>
+        <v>172.9</v>
       </c>
       <c r="D71">
-        <v>6977.38</v>
+        <v>-1983.8</v>
       </c>
       <c r="E71">
-        <v>1587271.54</v>
+        <v>314678</v>
       </c>
       <c r="F71" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>1587271.54</v>
+        <v>314678</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2762,28 +2723,28 @@
         <v>60</v>
       </c>
       <c r="B72">
-        <v>8907</v>
+        <v>66900</v>
       </c>
       <c r="C72">
-        <v>213.17</v>
+        <v>21.36</v>
       </c>
       <c r="D72">
-        <v>-30640.08</v>
+        <v>-17808.53</v>
       </c>
       <c r="E72">
-        <v>1898705.19</v>
+        <v>1428984</v>
       </c>
       <c r="F72" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G72" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I72">
-        <v>1898705.19</v>
+        <v>1118751.57</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2791,28 +2752,28 @@
         <v>61</v>
       </c>
       <c r="B73">
-        <v>18100</v>
+        <v>143200</v>
       </c>
       <c r="C73">
-        <v>41.17</v>
+        <v>31.52</v>
       </c>
       <c r="D73">
-        <v>-543</v>
+        <v>-48688</v>
       </c>
       <c r="E73">
-        <v>745177</v>
+        <v>4513664</v>
       </c>
       <c r="F73" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>745177</v>
+        <v>4513664</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2820,28 +2781,28 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>100</v>
+        <v>10700</v>
       </c>
       <c r="C74">
-        <v>63.55</v>
+        <v>99.95</v>
       </c>
       <c r="D74">
-        <v>80</v>
+        <v>-4708</v>
       </c>
       <c r="E74">
-        <v>6355</v>
+        <v>1069465</v>
       </c>
       <c r="F74" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>6355</v>
+        <v>1069465</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2849,28 +2810,28 @@
         <v>63</v>
       </c>
       <c r="B75">
-        <v>34</v>
+        <v>7000</v>
       </c>
       <c r="C75">
-        <v>180.99</v>
+        <v>68.08</v>
       </c>
       <c r="D75">
-        <v>-64.94</v>
+        <v>1120</v>
       </c>
       <c r="E75">
-        <v>6153.66</v>
+        <v>476560</v>
       </c>
       <c r="F75" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>6153.66</v>
+        <v>476560</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2878,28 +2839,28 @@
         <v>64</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>20100</v>
       </c>
       <c r="C76">
-        <v>106.8666</v>
+        <v>3.81</v>
       </c>
       <c r="D76">
-        <v>-11.3</v>
+        <v>-3015</v>
       </c>
       <c r="E76">
-        <v>1068.67</v>
+        <v>76581</v>
       </c>
       <c r="F76" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>1068.67</v>
+        <v>76581</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2907,28 +2868,28 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <v>18017</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>141.18</v>
+        <v>245.73</v>
       </c>
       <c r="D77">
-        <v>-34592.64</v>
+        <v>-5.5</v>
       </c>
       <c r="E77">
-        <v>2543640.06</v>
+        <v>491.46</v>
       </c>
       <c r="F77" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>2543640.06</v>
+        <v>491.46</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2936,28 +2897,28 @@
         <v>66</v>
       </c>
       <c r="B78">
-        <v>8810</v>
+        <v>51700</v>
       </c>
       <c r="C78">
-        <v>165.89</v>
+        <v>36.17</v>
       </c>
       <c r="D78">
-        <v>43961.9</v>
+        <v>809.55</v>
       </c>
       <c r="E78">
-        <v>1461490.9</v>
+        <v>1869989</v>
       </c>
       <c r="F78" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I78">
-        <v>1461490.9</v>
+        <v>1464014.39</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2965,28 +2926,28 @@
         <v>67</v>
       </c>
       <c r="B79">
-        <v>24680</v>
+        <v>503600</v>
       </c>
       <c r="C79">
-        <v>657.55</v>
+        <v>6.68</v>
       </c>
       <c r="D79">
-        <v>-164862.4</v>
+        <v>11828.51</v>
       </c>
       <c r="E79">
-        <v>16228334</v>
+        <v>3364048</v>
       </c>
       <c r="F79" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I79">
-        <v>16228334</v>
+        <v>2633713.18</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2994,28 +2955,28 @@
         <v>68</v>
       </c>
       <c r="B80">
-        <v>3800</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>56.11</v>
+        <v>94.36</v>
       </c>
       <c r="D80">
-        <v>-5358</v>
+        <v>-0.22</v>
       </c>
       <c r="E80">
-        <v>213218</v>
+        <v>94.36</v>
       </c>
       <c r="F80" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>213218</v>
+        <v>94.36</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3023,28 +2984,28 @@
         <v>69</v>
       </c>
       <c r="B81">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="C81">
-        <v>97.91</v>
+        <v>169.25</v>
       </c>
       <c r="D81">
-        <v>-27360</v>
+        <v>2768</v>
       </c>
       <c r="E81">
-        <v>881190</v>
+        <v>270800</v>
       </c>
       <c r="F81" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G81" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>881190</v>
+        <v>270800</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3052,28 +3013,28 @@
         <v>70</v>
       </c>
       <c r="B82">
-        <v>1820</v>
+        <v>6000</v>
       </c>
       <c r="C82">
-        <v>175.68</v>
+        <v>25.85</v>
       </c>
       <c r="D82">
-        <v>4186</v>
+        <v>-2151.6</v>
       </c>
       <c r="E82">
-        <v>319737.6</v>
+        <v>155100</v>
       </c>
       <c r="F82" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>319737.6</v>
+        <v>155100</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3081,28 +3042,28 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>66900</v>
+        <v>21</v>
       </c>
       <c r="C83">
-        <v>21.55</v>
+        <v>330.97</v>
       </c>
       <c r="D83">
-        <v>-4714.92</v>
+        <v>55.86</v>
       </c>
       <c r="E83">
-        <v>1441695</v>
+        <v>6950.37</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G83" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H83">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I83">
-        <v>1128991.35</v>
+        <v>6950.37</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3110,28 +3071,28 @@
         <v>72</v>
       </c>
       <c r="B84">
-        <v>143200</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>31.31</v>
+        <v>160.85</v>
       </c>
       <c r="D84">
-        <v>25776</v>
+        <v>55.7</v>
       </c>
       <c r="E84">
-        <v>4483592</v>
+        <v>1608.5</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>4483592</v>
+        <v>1608.5</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3139,28 +3100,28 @@
         <v>73</v>
       </c>
       <c r="B85">
-        <v>10700</v>
+        <v>6003</v>
       </c>
       <c r="C85">
-        <v>100.117</v>
+        <v>47.57</v>
       </c>
       <c r="D85">
-        <v>10774.9</v>
+        <v>-3241.62</v>
       </c>
       <c r="E85">
-        <v>1071251.9</v>
+        <v>285562.71</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1071251.9</v>
+        <v>285562.71</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3168,28 +3129,28 @@
         <v>74</v>
       </c>
       <c r="B86">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="C86">
-        <v>67.11</v>
+        <v>144.73</v>
       </c>
       <c r="D86">
-        <v>-2590</v>
+        <v>-8600</v>
       </c>
       <c r="E86">
-        <v>469770</v>
+        <v>2894600</v>
       </c>
       <c r="F86" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G86" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>469770</v>
+        <v>2894600</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3197,28 +3158,28 @@
         <v>75</v>
       </c>
       <c r="B87">
-        <v>20100</v>
+        <v>143300</v>
       </c>
       <c r="C87">
-        <v>3.73</v>
+        <v>4.67</v>
       </c>
       <c r="D87">
-        <v>-4020</v>
+        <v>8975.51</v>
       </c>
       <c r="E87">
-        <v>74973</v>
+        <v>669211</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.7829</v>
       </c>
       <c r="I87">
-        <v>74973</v>
+        <v>523925.29</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3226,28 +3187,28 @@
         <v>76</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>271664</v>
       </c>
       <c r="C88">
-        <v>239.71</v>
+        <v>20.8</v>
       </c>
       <c r="D88">
-        <v>-7.18</v>
+        <v>-43466.24</v>
       </c>
       <c r="E88">
-        <v>479.42</v>
+        <v>5650611.2</v>
       </c>
       <c r="F88" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G88" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>479.42</v>
+        <v>5650611.2</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3255,28 +3216,28 @@
         <v>77</v>
       </c>
       <c r="B89">
-        <v>51700</v>
+        <v>224882</v>
       </c>
       <c r="C89">
-        <v>35.96</v>
+        <v>25.27</v>
       </c>
       <c r="D89">
-        <v>2429.11</v>
+        <v>-33732.3</v>
       </c>
       <c r="E89">
-        <v>1859132</v>
+        <v>5682768.14</v>
       </c>
       <c r="F89" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H89">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I89">
-        <v>1455886.27</v>
+        <v>5682768.14</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3284,28 +3245,28 @@
         <v>78</v>
       </c>
       <c r="B90">
-        <v>503600</v>
+        <v>485540</v>
       </c>
       <c r="C90">
-        <v>6.65</v>
+        <v>100.42</v>
       </c>
       <c r="D90">
-        <v>-31548.73</v>
+        <v>4855.4</v>
       </c>
       <c r="E90">
-        <v>3348940</v>
+        <v>48757926.8</v>
       </c>
       <c r="F90" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H90">
-        <v>0.7831</v>
+        <v>1</v>
       </c>
       <c r="I90">
-        <v>2622554.91</v>
+        <v>48757926.8</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3313,28 +3274,28 @@
         <v>79</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>1521</v>
       </c>
       <c r="C91">
-        <v>93.78</v>
+        <v>42.34</v>
       </c>
       <c r="D91">
-        <v>0.21</v>
+        <v>-182.52</v>
       </c>
       <c r="E91">
-        <v>93.78</v>
+        <v>64399.14</v>
       </c>
       <c r="F91" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G91" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91">
-        <v>93.78</v>
+        <v>64399.14</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3342,28 +3303,28 @@
         <v>80</v>
       </c>
       <c r="B92">
-        <v>1600</v>
+        <v>790</v>
       </c>
       <c r="C92">
-        <v>164.43</v>
+        <v>109.22</v>
       </c>
       <c r="D92">
-        <v>4064</v>
+        <v>-6541.2</v>
       </c>
       <c r="E92">
-        <v>263088</v>
+        <v>86283.8</v>
       </c>
       <c r="F92" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>263088</v>
+        <v>86283.8</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3371,28 +3332,28 @@
         <v>81</v>
       </c>
       <c r="B93">
-        <v>6000</v>
+        <v>59428</v>
       </c>
       <c r="C93">
-        <v>26.1501</v>
+        <v>45.01</v>
       </c>
       <c r="D93">
-        <v>3300.6</v>
+        <v>-55862.32</v>
       </c>
       <c r="E93">
-        <v>156900.6</v>
+        <v>2674854.28</v>
       </c>
       <c r="F93" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>156900.6</v>
+        <v>2674854.28</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3400,28 +3361,28 @@
         <v>82</v>
       </c>
       <c r="B94">
-        <v>21</v>
+        <v>6788</v>
       </c>
       <c r="C94">
-        <v>305.03</v>
+        <v>54.77</v>
       </c>
       <c r="D94">
-        <v>-365.4</v>
+        <v>-7263.16</v>
       </c>
       <c r="E94">
-        <v>6405.63</v>
+        <v>371778.76</v>
       </c>
       <c r="F94" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>6405.63</v>
+        <v>371778.76</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3429,28 +3390,28 @@
         <v>83</v>
       </c>
       <c r="B95">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C95">
-        <v>161.12</v>
+        <v>84.25</v>
       </c>
       <c r="D95">
-        <v>-54.6</v>
+        <v>67</v>
       </c>
       <c r="E95">
-        <v>1611.2</v>
+        <v>8425</v>
       </c>
       <c r="F95" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>1611.2</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3458,28 +3419,28 @@
         <v>84</v>
       </c>
       <c r="B96">
-        <v>6003</v>
+        <v>33850</v>
       </c>
       <c r="C96">
-        <v>47.24</v>
+        <v>59.39</v>
       </c>
       <c r="D96">
-        <v>840.42</v>
+        <v>18279</v>
       </c>
       <c r="E96">
-        <v>283581.72</v>
+        <v>2010351.5</v>
       </c>
       <c r="F96" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G96" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>283581.72</v>
+        <v>2010351.5</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3487,28 +3448,28 @@
         <v>85</v>
       </c>
       <c r="B97">
-        <v>20000</v>
+        <v>33</v>
       </c>
       <c r="C97">
-        <v>143.84</v>
+        <v>58.44</v>
       </c>
       <c r="D97">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>2876800</v>
+        <v>1928.52</v>
       </c>
       <c r="F97" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97">
-        <v>2876800</v>
+        <v>1928.52</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3516,402 +3477,25 @@
         <v>86</v>
       </c>
       <c r="B98">
-        <v>143300</v>
+        <v>333</v>
       </c>
       <c r="C98">
-        <v>4.6</v>
+        <v>0.89</v>
       </c>
       <c r="D98">
-        <v>-1122.15</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>659180</v>
+        <v>296.37</v>
       </c>
       <c r="F98" t="s">
-        <v>102</v>
-      </c>
-      <c r="G98" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="H98">
-        <v>0.7831</v>
+        <v>0.7829</v>
       </c>
       <c r="I98">
-        <v>516203.86</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" t="s">
-        <v>87</v>
-      </c>
-      <c r="B99">
-        <v>271664</v>
-      </c>
-      <c r="C99">
-        <v>21.09</v>
-      </c>
-      <c r="D99">
-        <v>-10866.56</v>
-      </c>
-      <c r="E99">
-        <v>5729393.76</v>
-      </c>
-      <c r="F99" t="s">
-        <v>103</v>
-      </c>
-      <c r="G99" t="s">
-        <v>105</v>
-      </c>
-      <c r="H99">
-        <v>1</v>
-      </c>
-      <c r="I99">
-        <v>5729393.76</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" t="s">
-        <v>88</v>
-      </c>
-      <c r="B100">
-        <v>224882</v>
-      </c>
-      <c r="C100">
-        <v>25.64</v>
-      </c>
-      <c r="D100">
-        <v>-8995.280000000001</v>
-      </c>
-      <c r="E100">
-        <v>5765974.48</v>
-      </c>
-      <c r="F100" t="s">
-        <v>103</v>
-      </c>
-      <c r="G100" t="s">
-        <v>105</v>
-      </c>
-      <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
-        <v>5765974.48</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" t="s">
-        <v>89</v>
-      </c>
-      <c r="B101">
-        <v>485340</v>
-      </c>
-      <c r="C101">
-        <v>100.66</v>
-      </c>
-      <c r="D101">
-        <v>9706.799999999999</v>
-      </c>
-      <c r="E101">
-        <v>48854324.4</v>
-      </c>
-      <c r="F101" t="s">
-        <v>103</v>
-      </c>
-      <c r="G101" t="s">
-        <v>105</v>
-      </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>48854324.4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" t="s">
-        <v>90</v>
-      </c>
-      <c r="B102">
-        <v>1521</v>
-      </c>
-      <c r="C102">
-        <v>42.64</v>
-      </c>
-      <c r="D102">
-        <v>-76.05</v>
-      </c>
-      <c r="E102">
-        <v>64855.44</v>
-      </c>
-      <c r="F102" t="s">
-        <v>103</v>
-      </c>
-      <c r="G102" t="s">
-        <v>105</v>
-      </c>
-      <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102">
-        <v>64855.44</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
-      <c r="A103" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103">
-        <v>5600</v>
-      </c>
-      <c r="C103">
-        <v>86.37</v>
-      </c>
-      <c r="D103">
-        <v>504</v>
-      </c>
-      <c r="E103">
-        <v>483672</v>
-      </c>
-      <c r="F103" t="s">
-        <v>103</v>
-      </c>
-      <c r="G103" t="s">
-        <v>105</v>
-      </c>
-      <c r="H103">
-        <v>1</v>
-      </c>
-      <c r="I103">
-        <v>483672</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" t="s">
-        <v>92</v>
-      </c>
-      <c r="B104">
-        <v>790</v>
-      </c>
-      <c r="C104">
-        <v>110.61</v>
-      </c>
-      <c r="D104">
-        <v>-5759.1</v>
-      </c>
-      <c r="E104">
-        <v>87381.89999999999</v>
-      </c>
-      <c r="F104" t="s">
-        <v>103</v>
-      </c>
-      <c r="G104" t="s">
-        <v>106</v>
-      </c>
-      <c r="H104">
-        <v>1</v>
-      </c>
-      <c r="I104">
-        <v>87381.89999999999</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" t="s">
-        <v>93</v>
-      </c>
-      <c r="B105">
-        <v>12103</v>
-      </c>
-      <c r="C105">
-        <v>88.54000000000001</v>
-      </c>
-      <c r="D105">
-        <v>-49017.15</v>
-      </c>
-      <c r="E105">
-        <v>1071599.62</v>
-      </c>
-      <c r="F105" t="s">
-        <v>103</v>
-      </c>
-      <c r="G105" t="s">
-        <v>106</v>
-      </c>
-      <c r="H105">
-        <v>1</v>
-      </c>
-      <c r="I105">
-        <v>1071599.62</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="A106" t="s">
-        <v>94</v>
-      </c>
-      <c r="B106">
-        <v>59428</v>
-      </c>
-      <c r="C106">
-        <v>45.8</v>
-      </c>
-      <c r="D106">
-        <v>-50513.8</v>
-      </c>
-      <c r="E106">
-        <v>2721802.4</v>
-      </c>
-      <c r="F106" t="s">
-        <v>103</v>
-      </c>
-      <c r="G106" t="s">
-        <v>106</v>
-      </c>
-      <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="I106">
-        <v>2721802.4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" t="s">
-        <v>95</v>
-      </c>
-      <c r="B107">
-        <v>6788</v>
-      </c>
-      <c r="C107">
-        <v>54.23</v>
-      </c>
-      <c r="D107">
-        <v>-16766.36</v>
-      </c>
-      <c r="E107">
-        <v>368113.24</v>
-      </c>
-      <c r="F107" t="s">
-        <v>103</v>
-      </c>
-      <c r="G107" t="s">
-        <v>106</v>
-      </c>
-      <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107">
-        <v>368113.24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="A108" t="s">
-        <v>96</v>
-      </c>
-      <c r="B108">
-        <v>100</v>
-      </c>
-      <c r="C108">
-        <v>83.02</v>
-      </c>
-      <c r="D108">
-        <v>-74</v>
-      </c>
-      <c r="E108">
-        <v>8302</v>
-      </c>
-      <c r="F108" t="s">
-        <v>103</v>
-      </c>
-      <c r="G108" t="s">
-        <v>106</v>
-      </c>
-      <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="I108">
-        <v>8302</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
-      <c r="A109" t="s">
-        <v>97</v>
-      </c>
-      <c r="B109">
-        <v>33850</v>
-      </c>
-      <c r="C109">
-        <v>57.71</v>
-      </c>
-      <c r="D109">
-        <v>31819</v>
-      </c>
-      <c r="E109">
-        <v>1953483.5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>103</v>
-      </c>
-      <c r="G109" t="s">
-        <v>106</v>
-      </c>
-      <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="I109">
-        <v>1953483.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="A110" t="s">
-        <v>98</v>
-      </c>
-      <c r="B110">
-        <v>33</v>
-      </c>
-      <c r="C110">
-        <v>57.5</v>
-      </c>
-      <c r="D110">
-        <v>-2.64</v>
-      </c>
-      <c r="E110">
-        <v>1897.5</v>
-      </c>
-      <c r="F110" t="s">
-        <v>103</v>
-      </c>
-      <c r="G110" t="s">
-        <v>107</v>
-      </c>
-      <c r="H110">
-        <v>1</v>
-      </c>
-      <c r="I110">
-        <v>1897.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="A111" t="s">
-        <v>99</v>
-      </c>
-      <c r="B111">
-        <v>333</v>
-      </c>
-      <c r="C111">
-        <v>0.89</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="E111">
-        <v>296.37</v>
-      </c>
-      <c r="F111" t="s">
-        <v>102</v>
-      </c>
-      <c r="H111">
-        <v>0.7831</v>
-      </c>
-      <c r="I111">
-        <v>232.09</v>
+        <v>232.03</v>
       </c>
     </row>
   </sheetData>

--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260501.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260501.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="96">
   <si>
     <t>Symbol</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>GEV</t>
+  </si>
+  <si>
+    <t>GIS</t>
   </si>
   <si>
     <t>HGER</t>
@@ -656,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -696,25 +699,25 @@
         <v>2000</v>
       </c>
       <c r="C2">
-        <v>33.04</v>
+        <v>32.5</v>
       </c>
       <c r="D2">
-        <v>137.88</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>66080</v>
+        <v>65000</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I2">
-        <v>8438.42</v>
+        <v>8294</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -725,25 +728,25 @@
         <v>427000</v>
       </c>
       <c r="C3">
-        <v>12.87</v>
+        <v>13.4</v>
       </c>
       <c r="D3">
-        <v>-28893</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5495490</v>
+        <v>5721800</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I3">
-        <v>701774.0699999999</v>
+        <v>730101.6800000001</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -754,25 +757,25 @@
         <v>6000</v>
       </c>
       <c r="C4">
-        <v>5.94</v>
+        <v>6.08</v>
       </c>
       <c r="D4">
-        <v>-107.24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35640</v>
+        <v>36480</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I4">
-        <v>4551.23</v>
+        <v>4654.85</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -783,25 +786,25 @@
         <v>6000</v>
       </c>
       <c r="C5">
-        <v>6.92</v>
+        <v>7.03</v>
       </c>
       <c r="D5">
-        <v>-84.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>41520</v>
+        <v>42180</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I5">
-        <v>5302.1</v>
+        <v>5382.17</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -812,25 +815,25 @@
         <v>2000</v>
       </c>
       <c r="C6">
-        <v>35.72</v>
+        <v>35.08</v>
       </c>
       <c r="D6">
-        <v>163.42</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>71440</v>
+        <v>70160</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I6">
-        <v>9122.889999999999</v>
+        <v>8952.42</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -841,25 +844,25 @@
         <v>200</v>
       </c>
       <c r="C7">
-        <v>30.98</v>
+        <v>29.02</v>
       </c>
       <c r="D7">
-        <v>50.05</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6196</v>
+        <v>5804</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I7">
-        <v>791.23</v>
+        <v>740.59</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -870,25 +873,25 @@
         <v>300</v>
       </c>
       <c r="C8">
-        <v>137.4</v>
+        <v>136</v>
       </c>
       <c r="D8">
-        <v>53.62</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>41220</v>
+        <v>40800</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I8">
-        <v>5263.79</v>
+        <v>5206.08</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -899,25 +902,25 @@
         <v>2000</v>
       </c>
       <c r="C9">
-        <v>26.24</v>
+        <v>25.9</v>
       </c>
       <c r="D9">
-        <v>86.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>52480</v>
+        <v>51800</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I9">
-        <v>6701.7</v>
+        <v>6609.68</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -928,25 +931,25 @@
         <v>600</v>
       </c>
       <c r="C10">
-        <v>89.98</v>
+        <v>88.88</v>
       </c>
       <c r="D10">
-        <v>84.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>53988</v>
+        <v>53328</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I10">
-        <v>6894.27</v>
+        <v>6804.65</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -957,25 +960,25 @@
         <v>110000</v>
       </c>
       <c r="C11">
-        <v>35.8</v>
+        <v>35.68</v>
       </c>
       <c r="D11">
-        <v>1685.24</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>3938000</v>
+        <v>3924800</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I11">
-        <v>502882.6</v>
+        <v>500804.48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -986,25 +989,25 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>10.46</v>
+        <v>10.26</v>
       </c>
       <c r="D12">
-        <v>17.87</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>7322</v>
+        <v>7182</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I12">
-        <v>935.02</v>
+        <v>916.42</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1015,25 +1018,25 @@
         <v>4700</v>
       </c>
       <c r="C13">
-        <v>631.5</v>
+        <v>608</v>
       </c>
       <c r="D13">
-        <v>14101.15</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>2968050</v>
+        <v>2857600</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I13">
-        <v>379019.99</v>
+        <v>364629.76</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1044,25 +1047,25 @@
         <v>23500</v>
       </c>
       <c r="C14">
-        <v>415</v>
+        <v>412.4</v>
       </c>
       <c r="D14">
-        <v>7800.64</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>9752500</v>
+        <v>9691400</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I14">
-        <v>1245394.25</v>
+        <v>1236622.64</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1073,25 +1076,25 @@
         <v>4000</v>
       </c>
       <c r="C15">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="D15">
-        <v>15.32</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>20360</v>
+        <v>20240</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I15">
-        <v>2599.97</v>
+        <v>2582.62</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1105,16 +1108,16 @@
         <v>6514</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-9664.77</v>
       </c>
       <c r="E16">
         <v>229944200</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16">
         <v>0.0064</v>
@@ -1131,25 +1134,25 @@
         <v>200</v>
       </c>
       <c r="C17">
-        <v>473</v>
+        <v>467.8</v>
       </c>
       <c r="D17">
-        <v>132.78</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>94600</v>
+        <v>93560</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I17">
-        <v>12080.42</v>
+        <v>11938.26</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1160,25 +1163,25 @@
         <v>16000</v>
       </c>
       <c r="C18">
-        <v>7.34</v>
+        <v>7.32</v>
       </c>
       <c r="D18">
-        <v>40.85</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>117440</v>
+        <v>117120</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I18">
-        <v>14997.09</v>
+        <v>14944.51</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1192,16 +1195,16 @@
         <v>5390</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>133.71</v>
       </c>
       <c r="E19">
         <v>11319000</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19">
         <v>0.0064</v>
@@ -1218,25 +1221,25 @@
         <v>342000</v>
       </c>
       <c r="C20">
-        <v>11.7</v>
+        <v>12.03</v>
       </c>
       <c r="D20">
-        <v>-14408.84</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>4001400</v>
+        <v>4114260</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I20">
-        <v>510978.78</v>
+        <v>524979.58</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1247,25 +1250,25 @@
         <v>106000</v>
       </c>
       <c r="C21">
-        <v>28.62</v>
+        <v>29.38</v>
       </c>
       <c r="D21">
-        <v>-10285.1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>3033720</v>
+        <v>3114280</v>
       </c>
       <c r="F21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I21">
-        <v>387406.04</v>
+        <v>397382.13</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1276,25 +1279,25 @@
         <v>1800</v>
       </c>
       <c r="C22">
-        <v>46.36</v>
+        <v>46.8</v>
       </c>
       <c r="D22">
-        <v>-101.11</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>83448</v>
+        <v>84240</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I22">
-        <v>10656.31</v>
+        <v>10749.02</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1305,25 +1308,25 @@
         <v>6000</v>
       </c>
       <c r="C23">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="D23">
-        <v>93.95</v>
+        <v>161.98</v>
       </c>
       <c r="E23">
-        <v>15060</v>
+        <v>14940</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23">
-        <v>0.7829</v>
+        <v>0.7852</v>
       </c>
       <c r="I23">
-        <v>11790.47</v>
+        <v>11730.89</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1334,25 +1337,25 @@
         <v>1362</v>
       </c>
       <c r="C24">
-        <v>180.26</v>
+        <v>184.97</v>
       </c>
       <c r="D24">
-        <v>-6415.02</v>
+        <v>-13688.1</v>
       </c>
       <c r="E24">
-        <v>245514.12</v>
+        <v>251929.14</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>245514.12</v>
+        <v>251929.14</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1363,25 +1366,25 @@
         <v>18900</v>
       </c>
       <c r="C25">
-        <v>104.74</v>
+        <v>105.61</v>
       </c>
       <c r="D25">
-        <v>-16443</v>
+        <v>-10206</v>
       </c>
       <c r="E25">
-        <v>1979586</v>
+        <v>1996029</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>1979586</v>
+        <v>1996029</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1392,25 +1395,25 @@
         <v>22075</v>
       </c>
       <c r="C26">
-        <v>90.38</v>
+        <v>90.53</v>
       </c>
       <c r="D26">
-        <v>-3311.25</v>
+        <v>3752.75</v>
       </c>
       <c r="E26">
-        <v>1995138.5</v>
+        <v>1998449.75</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1995138.5</v>
+        <v>1998449.75</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1421,25 +1424,25 @@
         <v>14660</v>
       </c>
       <c r="C27">
-        <v>118.56</v>
+        <v>119.96</v>
       </c>
       <c r="D27">
-        <v>-20524</v>
+        <v>-2638.8</v>
       </c>
       <c r="E27">
-        <v>1738089.6</v>
+        <v>1758613.6</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1738089.6</v>
+        <v>1758613.6</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1450,25 +1453,25 @@
         <v>14901</v>
       </c>
       <c r="C28">
-        <v>133.27</v>
+        <v>131.5</v>
       </c>
       <c r="D28">
-        <v>26374.77</v>
+        <v>-5662.38</v>
       </c>
       <c r="E28">
-        <v>1985856.27</v>
+        <v>1959481.5</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1985856.27</v>
+        <v>1959481.5</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1479,25 +1482,25 @@
         <v>70</v>
       </c>
       <c r="C29">
-        <v>22.79</v>
+        <v>21.88</v>
       </c>
       <c r="D29">
-        <v>63.7</v>
+        <v>33.6</v>
       </c>
       <c r="E29">
-        <v>1595.3</v>
+        <v>1531.6</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1595.3</v>
+        <v>1531.6</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1517,16 +1520,16 @@
         <v>32610</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30">
-        <v>0.7829</v>
+        <v>0.7852</v>
       </c>
       <c r="I30">
-        <v>25530.37</v>
+        <v>25605.37</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1537,25 +1540,25 @@
         <v>821</v>
       </c>
       <c r="C31">
-        <v>216.68</v>
+        <v>216.31</v>
       </c>
       <c r="D31">
-        <v>303.77</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="E31">
-        <v>177894.28</v>
+        <v>177590.51</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>177894.28</v>
+        <v>177590.51</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1566,25 +1569,25 @@
         <v>200</v>
       </c>
       <c r="C32">
-        <v>6.27</v>
+        <v>6.29</v>
       </c>
       <c r="D32">
-        <v>-3.13</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="F32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32">
-        <v>0.7829</v>
+        <v>0.7852</v>
       </c>
       <c r="I32">
-        <v>981.76</v>
+        <v>987.78</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1595,25 +1598,25 @@
         <v>15</v>
       </c>
       <c r="C33">
-        <v>321.05</v>
+        <v>307.81</v>
       </c>
       <c r="D33">
-        <v>198.6</v>
+        <v>-77.84999999999999</v>
       </c>
       <c r="E33">
-        <v>4815.75</v>
+        <v>4617.15</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>4815.75</v>
+        <v>4617.15</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1624,25 +1627,25 @@
         <v>659624</v>
       </c>
       <c r="C34">
-        <v>31.45</v>
+        <v>31.42</v>
       </c>
       <c r="D34">
-        <v>19788.72</v>
+        <v>85751.12</v>
       </c>
       <c r="E34">
-        <v>20745174.8</v>
+        <v>20725386.08</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>20745174.8</v>
+        <v>20725386.08</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1653,25 +1656,25 @@
         <v>29</v>
       </c>
       <c r="C35">
-        <v>290.29</v>
+        <v>289.54</v>
       </c>
       <c r="D35">
-        <v>21.75</v>
+        <v>49.88</v>
       </c>
       <c r="E35">
-        <v>8418.41</v>
+        <v>8396.66</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>8418.41</v>
+        <v>8396.66</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1682,25 +1685,25 @@
         <v>103455</v>
       </c>
       <c r="C36">
-        <v>52.88</v>
+        <v>53.39</v>
       </c>
       <c r="D36">
-        <v>-52762.05</v>
+        <v>34140.15</v>
       </c>
       <c r="E36">
-        <v>5470700.4</v>
+        <v>5523462.45</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>5470700.4</v>
+        <v>5523462.45</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1711,25 +1714,25 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>202.99</v>
+        <v>191.25</v>
       </c>
       <c r="D37">
-        <v>58.7</v>
+        <v>17.4</v>
       </c>
       <c r="E37">
-        <v>1014.95</v>
+        <v>956.25</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>1014.95</v>
+        <v>956.25</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1740,25 +1743,25 @@
         <v>45862</v>
       </c>
       <c r="C38">
-        <v>37.45</v>
+        <v>38.23</v>
       </c>
       <c r="D38">
-        <v>-35772.36</v>
+        <v>-16510.32</v>
       </c>
       <c r="E38">
-        <v>1717531.9</v>
+        <v>1753304.26</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1717531.9</v>
+        <v>1753304.26</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1769,25 +1772,25 @@
         <v>13</v>
       </c>
       <c r="C39">
-        <v>92.63</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="D39">
-        <v>10.14</v>
+        <v>4.55</v>
       </c>
       <c r="E39">
-        <v>1204.19</v>
+        <v>1194.05</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>1204.19</v>
+        <v>1194.05</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1798,25 +1801,25 @@
         <v>10</v>
       </c>
       <c r="C40">
-        <v>166.89</v>
+        <v>169.61</v>
       </c>
       <c r="D40">
-        <v>-27.2</v>
+        <v>-51</v>
       </c>
       <c r="E40">
-        <v>1668.9</v>
+        <v>1696.1</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1668.9</v>
+        <v>1696.1</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1827,25 +1830,25 @@
         <v>361</v>
       </c>
       <c r="C41">
-        <v>192.28</v>
+        <v>190.63</v>
       </c>
       <c r="D41">
-        <v>595.65</v>
+        <v>-967.48</v>
       </c>
       <c r="E41">
-        <v>69413.08</v>
+        <v>68817.42999999999</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>69413.08</v>
+        <v>68817.42999999999</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1856,25 +1859,25 @@
         <v>800</v>
       </c>
       <c r="C42">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="D42">
-        <v>62.63</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>46880</v>
+        <v>46800</v>
       </c>
       <c r="F42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42">
-        <v>0.7829</v>
+        <v>0.7852</v>
       </c>
       <c r="I42">
-        <v>36702.35</v>
+        <v>36747.36</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1885,25 +1888,25 @@
         <v>612026</v>
       </c>
       <c r="C43">
-        <v>30.7</v>
+        <v>30.53</v>
       </c>
       <c r="D43">
-        <v>104044.42</v>
+        <v>-18360.78</v>
       </c>
       <c r="E43">
-        <v>18789198.2</v>
+        <v>18685153.78</v>
       </c>
       <c r="F43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>18789198.2</v>
+        <v>18685153.78</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1914,25 +1917,25 @@
         <v>401</v>
       </c>
       <c r="C44">
-        <v>578.39</v>
+        <v>577.26</v>
       </c>
       <c r="D44">
-        <v>453.13</v>
+        <v>-5056.61</v>
       </c>
       <c r="E44">
-        <v>231934.39</v>
+        <v>231481.26</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>231934.39</v>
+        <v>231481.26</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1943,25 +1946,25 @@
         <v>5000</v>
       </c>
       <c r="C45">
-        <v>114.48</v>
+        <v>114.43</v>
       </c>
       <c r="D45">
-        <v>250</v>
+        <v>-7250</v>
       </c>
       <c r="E45">
-        <v>572400</v>
+        <v>572150</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>572400</v>
+        <v>572150</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1972,25 +1975,25 @@
         <v>1</v>
       </c>
       <c r="C46">
-        <v>100.7</v>
+        <v>102.1</v>
       </c>
       <c r="D46">
-        <v>-1.4</v>
+        <v>-0.22</v>
       </c>
       <c r="E46">
-        <v>100.7</v>
+        <v>102.1</v>
       </c>
       <c r="F46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>100.7</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2001,25 +2004,25 @@
         <v>36</v>
       </c>
       <c r="C47">
-        <v>135.46</v>
+        <v>137.45</v>
       </c>
       <c r="D47">
-        <v>-71.64</v>
+        <v>-107.64</v>
       </c>
       <c r="E47">
-        <v>4876.56</v>
+        <v>4948.2</v>
       </c>
       <c r="F47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>4876.56</v>
+        <v>4948.2</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2030,25 +2033,25 @@
         <v>17</v>
       </c>
       <c r="C48">
-        <v>422.44</v>
+        <v>425.55</v>
       </c>
       <c r="D48">
-        <v>-52.87</v>
+        <v>-126.82</v>
       </c>
       <c r="E48">
-        <v>7181.48</v>
+        <v>7234.35</v>
       </c>
       <c r="F48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7181.48</v>
+        <v>7234.35</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2059,25 +2062,25 @@
         <v>30900</v>
       </c>
       <c r="C49">
-        <v>163.59</v>
+        <v>162</v>
       </c>
       <c r="D49">
-        <v>49131</v>
+        <v>38316</v>
       </c>
       <c r="E49">
-        <v>5054931</v>
+        <v>5005800</v>
       </c>
       <c r="F49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>5054931</v>
+        <v>5005800</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2088,25 +2091,25 @@
         <v>76000</v>
       </c>
       <c r="C50">
-        <v>39.04</v>
+        <v>39.43</v>
       </c>
       <c r="D50">
-        <v>-29640</v>
+        <v>-20520</v>
       </c>
       <c r="E50">
-        <v>2967040</v>
+        <v>2996680</v>
       </c>
       <c r="F50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>2967040</v>
+        <v>2996680</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2117,25 +2120,25 @@
         <v>1662</v>
       </c>
       <c r="C51">
-        <v>1073.95</v>
+        <v>1062.95</v>
       </c>
       <c r="D51">
-        <v>18282</v>
+        <v>-34087.62</v>
       </c>
       <c r="E51">
-        <v>1784904.9</v>
+        <v>1766622.9</v>
       </c>
       <c r="F51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1784904.9</v>
+        <v>1766622.9</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2143,28 +2146,28 @@
         <v>40</v>
       </c>
       <c r="B52">
-        <v>626620</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>32.69</v>
+        <v>34.72</v>
       </c>
       <c r="D52">
-        <v>206784.6</v>
+        <v>9095.1</v>
       </c>
       <c r="E52">
-        <v>20484207.8</v>
+        <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>20484207.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2172,28 +2175,28 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>42</v>
+        <v>626620</v>
       </c>
       <c r="C53">
-        <v>156.44</v>
+        <v>32.36</v>
       </c>
       <c r="D53">
-        <v>70.98</v>
+        <v>-140275.31</v>
       </c>
       <c r="E53">
-        <v>6570.48</v>
+        <v>20277423.2</v>
       </c>
       <c r="F53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53">
-        <v>6570.48</v>
+        <v>20277423.2</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2201,28 +2204,28 @@
         <v>42</v>
       </c>
       <c r="B54">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C54">
-        <v>307.65</v>
+        <v>154.75</v>
       </c>
       <c r="D54">
-        <v>-96.40000000000001</v>
+        <v>-140.28</v>
       </c>
       <c r="E54">
-        <v>6153</v>
+        <v>6499.5</v>
       </c>
       <c r="F54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>6153</v>
+        <v>6499.5</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2230,28 +2233,28 @@
         <v>43</v>
       </c>
       <c r="B55">
-        <v>611583</v>
+        <v>20</v>
       </c>
       <c r="C55">
-        <v>29.46</v>
+        <v>312.47</v>
       </c>
       <c r="D55">
-        <v>79505.78999999999</v>
+        <v>-15.2</v>
       </c>
       <c r="E55">
-        <v>18017235.18</v>
+        <v>6249.4</v>
       </c>
       <c r="F55" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55">
-        <v>18017235.18</v>
+        <v>6249.4</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2259,28 +2262,28 @@
         <v>44</v>
       </c>
       <c r="B56">
-        <v>3800</v>
+        <v>611583</v>
       </c>
       <c r="C56">
-        <v>621.77</v>
+        <v>29.33</v>
       </c>
       <c r="D56">
-        <v>72542</v>
+        <v>-177514.99</v>
       </c>
       <c r="E56">
-        <v>2362726</v>
+        <v>17937729.39</v>
       </c>
       <c r="F56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>2362726</v>
+        <v>17937729.39</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2288,28 +2291,28 @@
         <v>45</v>
       </c>
       <c r="B57">
-        <v>1451</v>
+        <v>3800</v>
       </c>
       <c r="C57">
-        <v>68.98999999999999</v>
+        <v>602.6799999999999</v>
       </c>
       <c r="D57">
-        <v>-1204.33</v>
+        <v>56696</v>
       </c>
       <c r="E57">
-        <v>100104.49</v>
+        <v>2290184</v>
       </c>
       <c r="F57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>100104.49</v>
+        <v>2290184</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2317,28 +2320,28 @@
         <v>46</v>
       </c>
       <c r="B58">
-        <v>1794</v>
+        <v>1451</v>
       </c>
       <c r="C58">
-        <v>5.54</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="D58">
-        <v>-304.98</v>
+        <v>-43.53</v>
       </c>
       <c r="E58">
-        <v>9938.76</v>
+        <v>101308.82</v>
       </c>
       <c r="F58" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>9938.76</v>
+        <v>101308.82</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2346,28 +2349,28 @@
         <v>47</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1794</v>
       </c>
       <c r="C59">
-        <v>967.9299999999999</v>
+        <v>5.71</v>
       </c>
       <c r="D59">
-        <v>13.8</v>
+        <v>-35.88</v>
       </c>
       <c r="E59">
-        <v>2903.79</v>
+        <v>10243.74</v>
       </c>
       <c r="F59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>2903.79</v>
+        <v>10243.74</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2375,28 +2378,28 @@
         <v>48</v>
       </c>
       <c r="B60">
-        <v>8000</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>1.96</v>
+        <v>963.33</v>
       </c>
       <c r="D60">
-        <v>-62.63</v>
+        <v>86.19</v>
       </c>
       <c r="E60">
-        <v>15680</v>
+        <v>2889.99</v>
       </c>
       <c r="F60" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H60">
-        <v>0.7829</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>12275.87</v>
+        <v>2889.99</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2404,28 +2407,28 @@
         <v>49</v>
       </c>
       <c r="B61">
-        <v>82</v>
+        <v>8000</v>
       </c>
       <c r="C61">
-        <v>1813.53</v>
+        <v>1.97</v>
       </c>
       <c r="D61">
-        <v>-2994.64</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>148709.46</v>
+        <v>15760</v>
       </c>
       <c r="F61" t="s">
         <v>90</v>
       </c>
       <c r="G61" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0.7852</v>
       </c>
       <c r="I61">
-        <v>148709.46</v>
+        <v>12374.75</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2433,28 +2436,28 @@
         <v>50</v>
       </c>
       <c r="B62">
-        <v>2747</v>
+        <v>82</v>
       </c>
       <c r="C62">
-        <v>567</v>
+        <v>1850.05</v>
       </c>
       <c r="D62">
-        <v>-3131.58</v>
+        <v>4708.44</v>
       </c>
       <c r="E62">
-        <v>1557549</v>
+        <v>151704.1</v>
       </c>
       <c r="F62" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>1557549</v>
+        <v>151704.1</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2462,28 +2465,28 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>18100</v>
+        <v>2747</v>
       </c>
       <c r="C63">
-        <v>44.39</v>
+        <v>568.14</v>
       </c>
       <c r="D63">
-        <v>9231</v>
+        <v>-31150.98</v>
       </c>
       <c r="E63">
-        <v>803459</v>
+        <v>1560680.58</v>
       </c>
       <c r="F63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>803459</v>
+        <v>1560680.58</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2491,28 +2494,28 @@
         <v>52</v>
       </c>
       <c r="B64">
-        <v>100</v>
+        <v>18100</v>
       </c>
       <c r="C64">
-        <v>63.45</v>
+        <v>43.88</v>
       </c>
       <c r="D64">
-        <v>-36</v>
+        <v>30046</v>
       </c>
       <c r="E64">
-        <v>6345</v>
+        <v>794228</v>
       </c>
       <c r="F64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>6345</v>
+        <v>794228</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2520,28 +2523,28 @@
         <v>53</v>
       </c>
       <c r="B65">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C65">
-        <v>184.56</v>
+        <v>63.81</v>
       </c>
       <c r="D65">
-        <v>118.32</v>
+        <v>-43</v>
       </c>
       <c r="E65">
-        <v>6275.04</v>
+        <v>6381</v>
       </c>
       <c r="F65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>6275.04</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2549,28 +2552,28 @@
         <v>54</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C66">
-        <v>107</v>
+        <v>181.08</v>
       </c>
       <c r="D66">
-        <v>-17.5</v>
+        <v>59.84</v>
       </c>
       <c r="E66">
-        <v>1070</v>
+        <v>6156.72</v>
       </c>
       <c r="F66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>1070</v>
+        <v>6156.72</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2578,28 +2581,28 @@
         <v>55</v>
       </c>
       <c r="B67">
-        <v>8810</v>
+        <v>10</v>
       </c>
       <c r="C67">
-        <v>169.19</v>
+        <v>108.75</v>
       </c>
       <c r="D67">
-        <v>24756.1</v>
+        <v>1.7</v>
       </c>
       <c r="E67">
-        <v>1490563.9</v>
+        <v>1087.5</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>1490563.9</v>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2607,28 +2610,28 @@
         <v>56</v>
       </c>
       <c r="B68">
-        <v>24680</v>
+        <v>8810</v>
       </c>
       <c r="C68">
-        <v>672.88</v>
+        <v>166.38</v>
       </c>
       <c r="D68">
-        <v>-31343.6</v>
+        <v>11541.1</v>
       </c>
       <c r="E68">
-        <v>16606678.4</v>
+        <v>1465807.8</v>
       </c>
       <c r="F68" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G68" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68">
-        <v>16606678.4</v>
+        <v>1465807.8</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2636,28 +2639,28 @@
         <v>57</v>
       </c>
       <c r="B69">
-        <v>3800</v>
+        <v>24680</v>
       </c>
       <c r="C69">
-        <v>47.57</v>
+        <v>674.15</v>
       </c>
       <c r="D69">
-        <v>9272</v>
+        <v>158198.8</v>
       </c>
       <c r="E69">
-        <v>180766</v>
+        <v>16638022</v>
       </c>
       <c r="F69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69">
-        <v>180766</v>
+        <v>16638022</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2665,28 +2668,28 @@
         <v>58</v>
       </c>
       <c r="B70">
-        <v>9000</v>
+        <v>3800</v>
       </c>
       <c r="C70">
-        <v>102.12</v>
+        <v>45.13</v>
       </c>
       <c r="D70">
-        <v>-39600</v>
+        <v>-38494</v>
       </c>
       <c r="E70">
-        <v>919080</v>
+        <v>171494</v>
       </c>
       <c r="F70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>919080</v>
+        <v>171494</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2694,28 +2697,28 @@
         <v>59</v>
       </c>
       <c r="B71">
-        <v>1820</v>
+        <v>9000</v>
       </c>
       <c r="C71">
-        <v>172.9</v>
+        <v>106.52</v>
       </c>
       <c r="D71">
-        <v>-1983.8</v>
+        <v>9810</v>
       </c>
       <c r="E71">
-        <v>314678</v>
+        <v>958680</v>
       </c>
       <c r="F71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>314678</v>
+        <v>958680</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2723,28 +2726,28 @@
         <v>60</v>
       </c>
       <c r="B72">
-        <v>66900</v>
+        <v>1820</v>
       </c>
       <c r="C72">
-        <v>21.36</v>
+        <v>173.99</v>
       </c>
       <c r="D72">
-        <v>-17808.53</v>
+        <v>-3785.6</v>
       </c>
       <c r="E72">
-        <v>1428984</v>
+        <v>316661.8</v>
       </c>
       <c r="F72" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H72">
-        <v>0.7829</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>1118751.57</v>
+        <v>316661.8</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2752,28 +2755,28 @@
         <v>61</v>
       </c>
       <c r="B73">
-        <v>143200</v>
+        <v>66900</v>
       </c>
       <c r="C73">
-        <v>31.52</v>
+        <v>21.7</v>
       </c>
       <c r="D73">
-        <v>-48688</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>4513664</v>
+        <v>1451730</v>
       </c>
       <c r="F73" t="s">
         <v>90</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.7852</v>
       </c>
       <c r="I73">
-        <v>4513664</v>
+        <v>1139898.4</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2781,28 +2784,28 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>10700</v>
+        <v>143200</v>
       </c>
       <c r="C74">
-        <v>99.95</v>
+        <v>31.86</v>
       </c>
       <c r="D74">
-        <v>-4708</v>
+        <v>-30072</v>
       </c>
       <c r="E74">
-        <v>1069465</v>
+        <v>4562352</v>
       </c>
       <c r="F74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>1069465</v>
+        <v>4562352</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2810,28 +2813,28 @@
         <v>63</v>
       </c>
       <c r="B75">
-        <v>7000</v>
+        <v>10700</v>
       </c>
       <c r="C75">
-        <v>68.08</v>
+        <v>100.39</v>
       </c>
       <c r="D75">
-        <v>1120</v>
+        <v>-5778</v>
       </c>
       <c r="E75">
-        <v>476560</v>
+        <v>1074173</v>
       </c>
       <c r="F75" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>476560</v>
+        <v>1074173</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2839,28 +2842,28 @@
         <v>64</v>
       </c>
       <c r="B76">
-        <v>20100</v>
+        <v>7000</v>
       </c>
       <c r="C76">
-        <v>3.81</v>
+        <v>67.92</v>
       </c>
       <c r="D76">
-        <v>-3015</v>
+        <v>-2030</v>
       </c>
       <c r="E76">
-        <v>76581</v>
+        <v>475440</v>
       </c>
       <c r="F76" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G76" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>76581</v>
+        <v>475440</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2868,28 +2871,28 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>20100</v>
       </c>
       <c r="C77">
-        <v>245.73</v>
+        <v>3.96</v>
       </c>
       <c r="D77">
-        <v>-5.5</v>
+        <v>2010</v>
       </c>
       <c r="E77">
-        <v>491.46</v>
+        <v>79596</v>
       </c>
       <c r="F77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G77" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>491.46</v>
+        <v>79596</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2897,28 +2900,28 @@
         <v>66</v>
       </c>
       <c r="B78">
-        <v>51700</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>36.17</v>
+        <v>248.48</v>
       </c>
       <c r="D78">
-        <v>809.55</v>
+        <v>4.22</v>
       </c>
       <c r="E78">
-        <v>1869989</v>
+        <v>496.96</v>
       </c>
       <c r="F78" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H78">
-        <v>0.7829</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>1464014.39</v>
+        <v>496.96</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2926,28 +2929,28 @@
         <v>67</v>
       </c>
       <c r="B79">
-        <v>503600</v>
+        <v>51700</v>
       </c>
       <c r="C79">
-        <v>6.68</v>
+        <v>36.15</v>
       </c>
       <c r="D79">
-        <v>11828.51</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>3364048</v>
+        <v>1868955</v>
       </c>
       <c r="F79" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H79">
-        <v>0.7829</v>
+        <v>0.7852</v>
       </c>
       <c r="I79">
-        <v>2633713.18</v>
+        <v>1467503.47</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2955,28 +2958,28 @@
         <v>68</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>503600</v>
       </c>
       <c r="C80">
-        <v>94.36</v>
+        <v>6.65</v>
       </c>
       <c r="D80">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>94.36</v>
+        <v>3348940</v>
       </c>
       <c r="F80" t="s">
         <v>90</v>
       </c>
       <c r="G80" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0.7852</v>
       </c>
       <c r="I80">
-        <v>94.36</v>
+        <v>2629587.69</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2984,28 +2987,28 @@
         <v>69</v>
       </c>
       <c r="B81">
-        <v>1600</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>169.25</v>
+        <v>94.58</v>
       </c>
       <c r="D81">
-        <v>2768</v>
+        <v>-0.06</v>
       </c>
       <c r="E81">
-        <v>270800</v>
+        <v>94.58</v>
       </c>
       <c r="F81" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G81" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>270800</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3013,28 +3016,28 @@
         <v>70</v>
       </c>
       <c r="B82">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="C82">
-        <v>25.85</v>
+        <v>167.52</v>
       </c>
       <c r="D82">
-        <v>-2151.6</v>
+        <v>-3296</v>
       </c>
       <c r="E82">
-        <v>155100</v>
+        <v>268032</v>
       </c>
       <c r="F82" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>155100</v>
+        <v>268032</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3042,28 +3045,28 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>6000</v>
       </c>
       <c r="C83">
-        <v>330.97</v>
+        <v>26.2086</v>
       </c>
       <c r="D83">
-        <v>55.86</v>
+        <v>1551.6</v>
       </c>
       <c r="E83">
-        <v>6950.37</v>
+        <v>157251.6</v>
       </c>
       <c r="F83" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>6950.37</v>
+        <v>157251.6</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3071,28 +3074,28 @@
         <v>72</v>
       </c>
       <c r="B84">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C84">
-        <v>160.85</v>
+        <v>328.31</v>
       </c>
       <c r="D84">
-        <v>55.7</v>
+        <v>-3.78</v>
       </c>
       <c r="E84">
-        <v>1608.5</v>
+        <v>6894.51</v>
       </c>
       <c r="F84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1608.5</v>
+        <v>6894.51</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3100,28 +3103,28 @@
         <v>73</v>
       </c>
       <c r="B85">
-        <v>6003</v>
+        <v>10</v>
       </c>
       <c r="C85">
-        <v>47.57</v>
+        <v>155.28</v>
       </c>
       <c r="D85">
-        <v>-3241.62</v>
+        <v>-25.6</v>
       </c>
       <c r="E85">
-        <v>285562.71</v>
+        <v>1552.8</v>
       </c>
       <c r="F85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>285562.71</v>
+        <v>1552.8</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3129,28 +3132,28 @@
         <v>74</v>
       </c>
       <c r="B86">
-        <v>20000</v>
+        <v>6003</v>
       </c>
       <c r="C86">
-        <v>144.73</v>
+        <v>48.11</v>
       </c>
       <c r="D86">
-        <v>-8600</v>
+        <v>3453.23</v>
       </c>
       <c r="E86">
-        <v>2894600</v>
+        <v>288804.33</v>
       </c>
       <c r="F86" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>2894600</v>
+        <v>288804.33</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3158,28 +3161,28 @@
         <v>75</v>
       </c>
       <c r="B87">
-        <v>143300</v>
+        <v>20000</v>
       </c>
       <c r="C87">
-        <v>4.67</v>
+        <v>145.16</v>
       </c>
       <c r="D87">
-        <v>8975.51</v>
+        <v>-16600</v>
       </c>
       <c r="E87">
-        <v>669211</v>
+        <v>2903200</v>
       </c>
       <c r="F87" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H87">
-        <v>0.7829</v>
+        <v>1</v>
       </c>
       <c r="I87">
-        <v>523925.29</v>
+        <v>2903200</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3187,16 +3190,16 @@
         <v>76</v>
       </c>
       <c r="B88">
-        <v>271664</v>
+        <v>143300</v>
       </c>
       <c r="C88">
-        <v>20.8</v>
+        <v>4.59</v>
       </c>
       <c r="D88">
-        <v>-43466.24</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>5650611.2</v>
+        <v>657747</v>
       </c>
       <c r="F88" t="s">
         <v>90</v>
@@ -3205,10 +3208,10 @@
         <v>92</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>0.7852</v>
       </c>
       <c r="I88">
-        <v>5650611.2</v>
+        <v>516462.94</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3216,28 +3219,28 @@
         <v>77</v>
       </c>
       <c r="B89">
-        <v>224882</v>
+        <v>271664</v>
       </c>
       <c r="C89">
-        <v>25.27</v>
+        <v>20.96</v>
       </c>
       <c r="D89">
-        <v>-33732.3</v>
+        <v>-21733.12</v>
       </c>
       <c r="E89">
-        <v>5682768.14</v>
+        <v>5694077.44</v>
       </c>
       <c r="F89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>5682768.14</v>
+        <v>5694077.44</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3245,28 +3248,28 @@
         <v>78</v>
       </c>
       <c r="B90">
-        <v>485540</v>
+        <v>224882</v>
       </c>
       <c r="C90">
-        <v>100.42</v>
+        <v>25.42</v>
       </c>
       <c r="D90">
-        <v>4855.4</v>
+        <v>-31483.48</v>
       </c>
       <c r="E90">
-        <v>48757926.8</v>
+        <v>5716500.44</v>
       </c>
       <c r="F90" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>48757926.8</v>
+        <v>5716500.44</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3274,28 +3277,28 @@
         <v>79</v>
       </c>
       <c r="B91">
-        <v>1521</v>
+        <v>485540</v>
       </c>
       <c r="C91">
-        <v>42.34</v>
+        <v>100.41</v>
       </c>
       <c r="D91">
-        <v>-182.52</v>
+        <v>-126189.1</v>
       </c>
       <c r="E91">
-        <v>64399.14</v>
+        <v>48753071.4</v>
       </c>
       <c r="F91" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91">
-        <v>64399.14</v>
+        <v>48753071.4</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3303,19 +3306,19 @@
         <v>80</v>
       </c>
       <c r="B92">
-        <v>790</v>
+        <v>1521</v>
       </c>
       <c r="C92">
-        <v>109.22</v>
+        <v>42.46</v>
       </c>
       <c r="D92">
-        <v>-6541.2</v>
+        <v>-319.41</v>
       </c>
       <c r="E92">
-        <v>86283.8</v>
+        <v>64581.66</v>
       </c>
       <c r="F92" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s">
         <v>93</v>
@@ -3324,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>86283.8</v>
+        <v>64581.66</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3332,28 +3335,28 @@
         <v>81</v>
       </c>
       <c r="B93">
-        <v>59428</v>
+        <v>790</v>
       </c>
       <c r="C93">
-        <v>45.01</v>
+        <v>117.5</v>
       </c>
       <c r="D93">
-        <v>-55862.32</v>
+        <v>4273.9</v>
       </c>
       <c r="E93">
-        <v>2674854.28</v>
+        <v>92825</v>
       </c>
       <c r="F93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>2674854.28</v>
+        <v>92825</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3361,28 +3364,28 @@
         <v>82</v>
       </c>
       <c r="B94">
-        <v>6788</v>
+        <v>59428</v>
       </c>
       <c r="C94">
-        <v>54.77</v>
+        <v>45.95</v>
       </c>
       <c r="D94">
-        <v>-7263.16</v>
+        <v>-1782.84</v>
       </c>
       <c r="E94">
-        <v>371778.76</v>
+        <v>2730716.6</v>
       </c>
       <c r="F94" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>371778.76</v>
+        <v>2730716.6</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3390,28 +3393,28 @@
         <v>83</v>
       </c>
       <c r="B95">
-        <v>100</v>
+        <v>6788</v>
       </c>
       <c r="C95">
-        <v>84.25</v>
+        <v>55.84</v>
       </c>
       <c r="D95">
-        <v>67</v>
+        <v>-3937.04</v>
       </c>
       <c r="E95">
-        <v>8425</v>
+        <v>379041.92</v>
       </c>
       <c r="F95" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>8425</v>
+        <v>379041.92</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3419,28 +3422,28 @@
         <v>84</v>
       </c>
       <c r="B96">
-        <v>33850</v>
+        <v>100</v>
       </c>
       <c r="C96">
-        <v>59.39</v>
+        <v>83.58</v>
       </c>
       <c r="D96">
-        <v>18279</v>
+        <v>-55</v>
       </c>
       <c r="E96">
-        <v>2010351.5</v>
+        <v>8358</v>
       </c>
       <c r="F96" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>2010351.5</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3448,19 +3451,19 @@
         <v>85</v>
       </c>
       <c r="B97">
-        <v>33</v>
+        <v>33850</v>
       </c>
       <c r="C97">
-        <v>58.44</v>
+        <v>58.85</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>-27080</v>
       </c>
       <c r="E97">
-        <v>1928.52</v>
+        <v>1992072.5</v>
       </c>
       <c r="F97" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G97" t="s">
         <v>94</v>
@@ -3469,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>1928.52</v>
+        <v>1992072.5</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3477,25 +3480,54 @@
         <v>86</v>
       </c>
       <c r="B98">
+        <v>33</v>
+      </c>
+      <c r="C98">
+        <v>58.44</v>
+      </c>
+      <c r="D98">
+        <v>-6.27</v>
+      </c>
+      <c r="E98">
+        <v>1928.52</v>
+      </c>
+      <c r="F98" t="s">
+        <v>91</v>
+      </c>
+      <c r="G98" t="s">
+        <v>95</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>1928.52</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>87</v>
+      </c>
+      <c r="B99">
         <v>333</v>
       </c>
-      <c r="C98">
+      <c r="C99">
         <v>0.89</v>
       </c>
-      <c r="D98">
+      <c r="D99">
         <v>0</v>
       </c>
-      <c r="E98">
+      <c r="E99">
         <v>296.37</v>
       </c>
-      <c r="F98" t="s">
-        <v>89</v>
-      </c>
-      <c r="H98">
-        <v>0.7829</v>
-      </c>
-      <c r="I98">
-        <v>232.03</v>
+      <c r="F99" t="s">
+        <v>90</v>
+      </c>
+      <c r="H99">
+        <v>0.7852</v>
+      </c>
+      <c r="I99">
+        <v>232.71</v>
       </c>
     </row>
   </sheetData>
